--- a/mlef_pipeline/results/OS_6/SQUAMOUS/RWD_PYRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/OS_6/SQUAMOUS/RWD_PYRAD/rwd-only/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.60 ± 0.09</t>
+          <t>0.61 ± 0.09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.50 ± 0.06</t>
+          <t>0.49 ± 0.11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.56 ± 0.32</t>
+          <t>0.30 ± 0.14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.58 ± 0.33</t>
+          <t>0.84 ± 0.08</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.72 ± 0.20</t>
+          <t>0.63 ± 0.22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.81 ± 0.28</t>
+          <t>0.72 ± 0.31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>0.62</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F4" t="n">
